--- a/planilhas/Auditoria de Criativos - V4.xlsx
+++ b/planilhas/Auditoria de Criativos - V4.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -750,7 +750,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>•  Analisa somente o que está no ar hoje: campanha ativa e anúncio ativo. Histórico é outro trabalho.</t>
+          <t>•  Analisa tudo que consumiu verba na janela auditada — ativo ou pausado. Anterior à janela é outro trabalho.</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2. Colete APENAS o que está ativo — campanha ativa E anúncio ativo. Meta: Biblioteca de Anúncios com o filtro Ativos (pública, não precisa de acesso). Google/TikTok/LinkedIn: gerenciador do cliente em modo somente leitura, com o filtro de status aplicado.</t>
+          <t>2. Colete tudo que GASTOU dentro da janela auditada — ativo ou pausado. Meta: Biblioteca de Anúncios (pública, não precisa de acesso). Google/TikTok/LinkedIn: gerenciador do cliente em modo somente leitura. Registre o status de cada peça na coluna Situação.</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>4. Ordene por gasto e audite de cima para baixo: as peças que somam ~80% da verba ATIVA são as que importam.</t>
+          <t>4. Ordene por gasto e audite de cima para baixo: as peças que somam ~80% da verba da janela são as que importam.</t>
         </is>
       </c>
     </row>
@@ -876,47 +876,54 @@
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>•  Só entra o que está ATIVO: campanha ativa e anúncio ativo, em qualquer rede. Peça pausada não recebe linha, não recebe veredito e não conta na verba analisada.</t>
+          <t>•  O corte é a JANELA, não o status: entra tudo que gastou no período auditado, ativo ou pausado. Peça pausada com gasto na janela é achado de processo — quanto queimou antes de pausarem. Peça sem gasto na janela fica fora.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>•  Anúncio ativo dentro de campanha pausada NÃO conta como ativo — confira os dois níveis antes de coletar.</t>
+          <t>•  Anúncio ativo dentro de campanha pausada NÃO está rodando — confira o status nos dois níveis e registre o mais restritivo.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>•  Todo veredito precisa de um porquê concreto. 'Criativo fraco' não é achado.</t>
+          <t>•  Todo achado sai rotulado: plataforma · onde foi visto · janela · valor · status. É o que permite conferir qualquer ponto na plataforma em 2 minutos.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>•  Métrica sem fonte não entra: registre de onde veio o número (export do gerenciador, período).</t>
+          <t>•  Todo veredito precisa de um porquê concreto. 'Criativo fraco' não é achado.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>•  Amostra pequena não vira taxa. Peça com 200 impressões não tem CTR confiável — marque como sem leitura.</t>
+          <t>•  Métrica sem fonte não entra: registre de onde veio o número (export do gerenciador, período).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>•  CTR bom com conversão ruim quase sempre é quebra entre anúncio e página de destino, não criativo ruim.</t>
+          <t>•  Amostra pequena não vira taxa. Peça com 200 impressões não tem CTR confiável — marque como sem leitura.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>•  CTR bom com conversão ruim quase sempre é quebra entre anúncio e página de destino, não criativo ruim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>•  Se a peça foi coletada da Biblioteca de Anúncios, você tem a peça mas não tem a métrica dela. Julgue o qualitativo e deixe as colunas de número vazias — não estime.</t>
         </is>
@@ -998,22 +1005,22 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Só campanha ativa e anúncio ativo entram</t>
+          <t>Entra tudo que gastou dentro da janela — ativo ou pausado</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Antes de julgar qualquer peça, confirme o status nos DOIS níveis: a campanha está ativa E o anúncio está ativo? Anúncio ativo dentro de campanha pausada não está rodando. No Meta, use o filtro Ativos da Biblioteca de Anúncios; nas demais redes, o filtro de status do gerenciador. No export, filtre por status antes de calcular qualquer percentual — gasto de campanha encerrada distorce a leitura de verba inteira.</t>
+          <t>O corte é o gasto na janela auditada (ex.: últimos 60 dias), não o status. Peça ativa recebe veredito de ação. Peça pausada dentro da janela entra como achado de processo: quanto queimou antes de pausarem e por quê — pausar não devolve o dinheiro (ex. real: termos de pesquisa ruins pausados na janela já tinham queimado ~R$ 500; caíram na auditoria). Confira o status nos dois níveis: anúncio ativo dentro de campanha pausada não está rodando. Peça sem gasto na janela fica fora.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>100% das peças auditadas com campanha e anúncio ativos</t>
+          <t>Janela definida no dossiê · status registrado em cada peça</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Remova da planilha o que estiver pausado. Se o cliente quiser a leitura do histórico (o que já foi testado), faça em documento separado e rotulado — nunca misturado aos achados da auditoria.</t>
+          <t>Preencha a coluna Situação em toda linha. O que for anterior à janela e o cliente quiser ver, vai em documento separado e rotulado — nunca misturado aos achados.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -9924,7 +9931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9933,8 +9940,9 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -9984,10 +9992,15 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Verba em "Matar"</t>
+          <t>Verba em "Matar" (ativos)</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Verba pausada na janela</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>% da verba em "Matar"</t>
         </is>
@@ -10020,10 +10033,14 @@
         <v/>
       </c>
       <c r="G4" s="22">
-        <f>SUMIF('Meta Ads'!$U$4:$U$33,"Matar",'Meta Ads'!$F$4:$F$33)</f>
+        <f>SUMIFS('Meta Ads'!$F$4:$F$33,'Meta Ads'!$U$4:$U$33,"Matar",'Meta Ads'!$E$4:$E$33,"Ativo")</f>
         <v/>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
+        <f>SUMIF('Meta Ads'!$E$4:$E$33,"Pausado na janela",'Meta Ads'!$F$4:$F$33)</f>
+        <v/>
+      </c>
+      <c r="I4" s="23">
         <f>IF(F4=0,0,G4/F4)</f>
         <v/>
       </c>
@@ -10055,10 +10072,14 @@
         <v/>
       </c>
       <c r="G5" s="26">
-        <f>SUMIF('Google Ads'!$U$4:$U$33,"Matar",'Google Ads'!$F$4:$F$33)</f>
+        <f>SUMIFS('Google Ads'!$F$4:$F$33,'Google Ads'!$U$4:$U$33,"Matar",'Google Ads'!$E$4:$E$33,"Ativo")</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="26">
+        <f>SUMIF('Google Ads'!$E$4:$E$33,"Pausado na janela",'Google Ads'!$F$4:$F$33)</f>
+        <v/>
+      </c>
+      <c r="I5" s="27">
         <f>IF(F5=0,0,G5/F5)</f>
         <v/>
       </c>
@@ -10090,10 +10111,14 @@
         <v/>
       </c>
       <c r="G6" s="22">
-        <f>SUMIF('TikTok Ads'!$U$4:$U$33,"Matar",'TikTok Ads'!$F$4:$F$33)</f>
+        <f>SUMIFS('TikTok Ads'!$F$4:$F$33,'TikTok Ads'!$U$4:$U$33,"Matar",'TikTok Ads'!$E$4:$E$33,"Ativo")</f>
         <v/>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="22">
+        <f>SUMIF('TikTok Ads'!$E$4:$E$33,"Pausado na janela",'TikTok Ads'!$F$4:$F$33)</f>
+        <v/>
+      </c>
+      <c r="I6" s="23">
         <f>IF(F6=0,0,G6/F6)</f>
         <v/>
       </c>
@@ -10125,10 +10150,14 @@
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>SUMIF('LinkedIn Ads'!$U$4:$U$33,"Matar",'LinkedIn Ads'!$F$4:$F$33)</f>
+        <f>SUMIFS('LinkedIn Ads'!$F$4:$F$33,'LinkedIn Ads'!$U$4:$U$33,"Matar",'LinkedIn Ads'!$E$4:$E$33,"Ativo")</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="26">
+        <f>SUMIF('LinkedIn Ads'!$E$4:$E$33,"Pausado na janela",'LinkedIn Ads'!$F$4:$F$33)</f>
+        <v/>
+      </c>
+      <c r="I7" s="27">
         <f>IF(F7=0,0,G7/F7)</f>
         <v/>
       </c>
@@ -10163,7 +10192,11 @@
         <f>SUM(G4:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="30">
+        <f>SUM(H4:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="31">
         <f>IF(F8=0,0,G8/F8)</f>
         <v/>
       </c>
@@ -10192,14 +10225,21 @@
     <row r="13">
       <c r="A13" s="33" t="inlineStr">
         <is>
-          <t>•  Verba analisada é a soma do gasto das peças auditadas — não é a verba total da conta, e não inclui campanha pausada. Registre a cobertura no relatório.</t>
+          <t>•  Verba analisada é a soma do gasto das peças auditadas na janela — ativas e pausadas. Não é a verba total da conta; registre a cobertura no relatório.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>•  Verba pausada na janela é dinheiro que já foi gasto em peça que saiu do ar dentro do período — o achado é de processo: quanto queimou antes de pausarem.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10254,7 +10294,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pausado durante a auditoria</t>
+          <t>Pausado na janela</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
